--- a/Clase/MSPS_Clase.xlsx
+++ b/Clase/MSPS_Clase.xlsx
@@ -680,13 +680,13 @@
         <v>1.749033107664364</v>
       </c>
       <c r="C2" s="2">
-        <v>107.3688831442312</v>
+        <v>107.3157204447852</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>1.877917313522067</v>
+        <v>1.876987480307828</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -788,7 +788,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="2">
-        <v>9.877069133136064</v>
+        <v>9.877069133136066</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1187,7 +1187,7 @@
         <v>36</v>
       </c>
       <c r="B32" s="2">
-        <v>1.815650530728368</v>
+        <v>1.815650530728367</v>
       </c>
       <c r="C32" s="2">
         <v>123.6899542106999</v>
@@ -1434,7 +1434,7 @@
         <v>6</v>
       </c>
       <c r="E46" s="2">
-        <v>0.7110152669897477</v>
+        <v>0.7110152669897478</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1527,7 +1527,7 @@
         <v>56</v>
       </c>
       <c r="B52" s="2">
-        <v>0.6213367053368656</v>
+        <v>0.6213367053368655</v>
       </c>
       <c r="C52" s="2">
         <v>104.8391659575252</v>
